--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_2_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_2_True.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Pg Vm Projection True</t>
   </si>
@@ -31,88 +31,91 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
     <t>pg_tot</t>
   </si>
   <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>28112.80 (23677.68 &gt; 18.78%)</t>
-  </si>
-  <si>
-    <t>1.38 (2.45)</t>
-  </si>
-  <si>
-    <t>0.21s (0.28 s)</t>
-  </si>
-  <si>
-    <t>24058.59 (23677.68 &gt; 1.61%)</t>
-  </si>
-  <si>
-    <t>2.25 (2.45)</t>
-  </si>
-  <si>
-    <t>0.13s (0.28 s)</t>
-  </si>
-  <si>
-    <t>23680.20 (23677.68 &gt; 0.01%)</t>
+    <t>0.48s (0.29 s)</t>
+  </si>
+  <si>
+    <t>1.49 (2.45)</t>
+  </si>
+  <si>
+    <t>28671.69 (24474.61 &gt; 17.15%)</t>
+  </si>
+  <si>
+    <t>0.11s (0.29 s)</t>
+  </si>
+  <si>
+    <t>2.24 (2.45)</t>
+  </si>
+  <si>
+    <t>24874.18 (24474.61 &gt; 1.63%)</t>
+  </si>
+  <si>
+    <t>0.29s (0.29 s)</t>
   </si>
   <si>
     <t>2.45 (2.45)</t>
   </si>
   <si>
-    <t>0.27s (0.28 s)</t>
-  </si>
-  <si>
-    <t>0.18s (0.28 s)</t>
+    <t>24477.39 (24474.61 &gt; 0.01%)</t>
+  </si>
+  <si>
+    <t>0.20s (0.29 s)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +498,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.179198902753544E-17</v>
+        <v>0.008228142745792866</v>
       </c>
       <c r="C2">
-        <v>1.179198902753544E-17</v>
+        <v>7.148268196033314E-05</v>
       </c>
       <c r="D2">
-        <v>1.179198902753544E-17</v>
+        <v>0.0001050427090376616</v>
       </c>
       <c r="E2">
-        <v>1.179198902753544E-17</v>
+        <v>7.805800123605877E-05</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,16 +515,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>8.651482582092285</v>
+        <v>0.3428511023521423</v>
       </c>
       <c r="C3">
-        <v>0.05632803961634636</v>
+        <v>0.003525395644828677</v>
       </c>
       <c r="D3">
-        <v>1.226379851004822E-07</v>
+        <v>0.003470288356766105</v>
       </c>
       <c r="E3">
-        <v>1.226379851004822E-07</v>
+        <v>0.002726080361753702</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -529,33 +532,33 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.002721101045608521</v>
+        <v>0.001281373901292682</v>
       </c>
       <c r="C4">
-        <v>0.004740309901535511</v>
+        <v>0.000194290914805606</v>
       </c>
       <c r="D4">
-        <v>0.0009043255704455078</v>
+        <v>0.0001508233835920691</v>
       </c>
       <c r="E4">
-        <v>0.0009043255704455078</v>
+        <v>0.0001427406241418794</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
+      <c r="B5">
+        <v>0.01334972772747278</v>
+      </c>
+      <c r="C5">
+        <v>0.005823848303407431</v>
+      </c>
+      <c r="D5">
+        <v>0.003171576885506511</v>
+      </c>
+      <c r="E5">
+        <v>0.002583921886980534</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +566,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.919338583946228</v>
+        <v>0.1242255419492722</v>
       </c>
       <c r="C6">
-        <v>0.006277100183069706</v>
+        <v>0.05246124044060707</v>
       </c>
       <c r="D6">
-        <v>4.557110059977276E-06</v>
+        <v>0.02763546444475651</v>
       </c>
       <c r="E6">
-        <v>4.557110059977276E-06</v>
+        <v>0.02132153511047363</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
+      <c r="B7">
+        <v>0.003270317334681749</v>
+      </c>
+      <c r="C7">
+        <v>0.001273308647796512</v>
+      </c>
+      <c r="D7">
+        <v>0.0030292181763798</v>
+      </c>
+      <c r="E7">
+        <v>0.002757957670837641</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,33 +600,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.007431769277900457</v>
+        <v>0.003181142965331674</v>
       </c>
       <c r="C8">
-        <v>4.0264905692311E-05</v>
+        <v>0.001437944476492703</v>
       </c>
       <c r="D8">
-        <v>6.562452654179651E-06</v>
+        <v>0.001170829753391445</v>
       </c>
       <c r="E8">
-        <v>6.562452654179651E-06</v>
+        <v>0.0009367818129248917</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
-        <v>0.1025990769267082</v>
-      </c>
-      <c r="C9">
-        <v>0.04644132032990456</v>
-      </c>
-      <c r="D9">
-        <v>0.004765178542584181</v>
-      </c>
-      <c r="E9">
-        <v>0.004765178542584181</v>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,50 +634,38 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.002070246729999781</v>
+        <v>0.003141723573207855</v>
       </c>
       <c r="C10">
-        <v>0.001365027623251081</v>
+        <v>0.001426592469215393</v>
       </c>
       <c r="D10">
-        <v>0.0004964048275724053</v>
+        <v>0.001159712206572294</v>
       </c>
       <c r="E10">
-        <v>0.0004964048275724053</v>
+        <v>0.000926701701246202</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="C11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="D11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="E11">
-        <v>6.066369421523152E-19</v>
-      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.9309866428375244</v>
+        <v>0.0001613140775589272</v>
       </c>
       <c r="C12">
-        <v>0.006630013231188059</v>
+        <v>0.0001080150686902925</v>
       </c>
       <c r="D12">
-        <v>1.290111661944593E-08</v>
+        <v>0.0001662411377765238</v>
       </c>
       <c r="E12">
-        <v>1.290111661944593E-08</v>
+        <v>0.0001348755467915908</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +673,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.3342661261558533</v>
+        <v>0.9414292573928833</v>
       </c>
       <c r="C13">
-        <v>0.0022479307372123</v>
+        <v>0.01058178301900625</v>
       </c>
       <c r="D13">
-        <v>4.458616331248777E-06</v>
+        <v>0.008671029470860958</v>
       </c>
       <c r="E13">
-        <v>4.458616331248777E-06</v>
+        <v>0.006613724865019321</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,50 +690,50 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.001337319263257086</v>
+        <v>0.9315747022628784</v>
       </c>
       <c r="C14">
-        <v>0.00019324358436279</v>
+        <v>0.009832382202148438</v>
       </c>
       <c r="D14">
-        <v>0.0001116096900659613</v>
+        <v>0.008339508436620235</v>
       </c>
       <c r="E14">
-        <v>0.0001116096900659613</v>
+        <v>0.006533988751471043</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.002039699116721749</v>
-      </c>
-      <c r="C15">
-        <v>0.001356336753815413</v>
-      </c>
-      <c r="D15">
-        <v>0.0004885719972662628</v>
-      </c>
-      <c r="E15">
-        <v>0.0004885719972662628</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.3348852396011353</v>
-      </c>
-      <c r="C16">
-        <v>0.002248478122055531</v>
-      </c>
-      <c r="D16">
-        <v>4.45091791334562E-06</v>
-      </c>
-      <c r="E16">
-        <v>4.45091791334562E-06</v>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,33 +741,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01110085565596819</v>
+        <v>0.34349125623703</v>
       </c>
       <c r="C17">
-        <v>0.005362888798117638</v>
+        <v>0.003523198422044516</v>
       </c>
       <c r="D17">
-        <v>0.0008567528566345572</v>
+        <v>0.003469370305538177</v>
       </c>
       <c r="E17">
-        <v>0.0008567528566345572</v>
+        <v>0.002725412836298347</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
+      <c r="B18">
+        <v>8.791230201721191</v>
+      </c>
+      <c r="C18">
+        <v>0.1119532585144043</v>
+      </c>
+      <c r="D18">
+        <v>0.09746880084276199</v>
+      </c>
+      <c r="E18">
+        <v>0.07025667279958725</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +775,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.001102066482417285</v>
+        <v>0.005500739440321922</v>
       </c>
       <c r="C19">
-        <v>0.0001988977455766872</v>
+        <v>0.004854017402976751</v>
       </c>
       <c r="D19">
-        <v>0.0001138017687480897</v>
+        <v>0.003025812562555075</v>
       </c>
       <c r="E19">
-        <v>0.0001138017687480897</v>
+        <v>0.002277159597724676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.001024813740514219</v>
+      </c>
+      <c r="C20">
+        <v>0.0001973032631212845</v>
+      </c>
+      <c r="D20">
+        <v>0.0001489240385126323</v>
+      </c>
+      <c r="E20">
+        <v>0.000140699150506407</v>
       </c>
     </row>
   </sheetData>
